--- a/catalogue/sessions.xlsx
+++ b/catalogue/sessions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vaibhavgurjar/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9F54CDDE-741C-304F-BB58-E40EFAE11C1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9F36A24-C2A8-E94B-A850-1F4FC4165C6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="580" windowWidth="28800" windowHeight="16260" xr2:uid="{5C538A93-F245-C740-BD91-3CC6C517ED2A}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="49">
   <si>
     <r>
       <t>Subject</t>
@@ -152,123 +152,6 @@
     <t>I6</t>
   </si>
   <si>
-    <t>A7</t>
-  </si>
-  <si>
-    <t>B7</t>
-  </si>
-  <si>
-    <t>I7</t>
-  </si>
-  <si>
-    <t>A8</t>
-  </si>
-  <si>
-    <t>B8</t>
-  </si>
-  <si>
-    <t>I8</t>
-  </si>
-  <si>
-    <t>A9</t>
-  </si>
-  <si>
-    <t>B9</t>
-  </si>
-  <si>
-    <t>I9</t>
-  </si>
-  <si>
-    <t>A10</t>
-  </si>
-  <si>
-    <t>B10</t>
-  </si>
-  <si>
-    <t>I10</t>
-  </si>
-  <si>
-    <t>A11</t>
-  </si>
-  <si>
-    <t>B11</t>
-  </si>
-  <si>
-    <t>I11</t>
-  </si>
-  <si>
-    <t>A12</t>
-  </si>
-  <si>
-    <t>B12</t>
-  </si>
-  <si>
-    <t>I12</t>
-  </si>
-  <si>
-    <t>A13</t>
-  </si>
-  <si>
-    <t>B13</t>
-  </si>
-  <si>
-    <t>I13</t>
-  </si>
-  <si>
-    <t>A14</t>
-  </si>
-  <si>
-    <t>B14</t>
-  </si>
-  <si>
-    <t>I14</t>
-  </si>
-  <si>
-    <t>A15</t>
-  </si>
-  <si>
-    <t>B15</t>
-  </si>
-  <si>
-    <t>I15</t>
-  </si>
-  <si>
-    <t>A16</t>
-  </si>
-  <si>
-    <t>B16</t>
-  </si>
-  <si>
-    <t>I16</t>
-  </si>
-  <si>
-    <t>A17</t>
-  </si>
-  <si>
-    <t>B17</t>
-  </si>
-  <si>
-    <t>I17</t>
-  </si>
-  <si>
-    <t>A18</t>
-  </si>
-  <si>
-    <t>B18</t>
-  </si>
-  <si>
-    <t>I18</t>
-  </si>
-  <si>
-    <t>A19</t>
-  </si>
-  <si>
-    <t>B19</t>
-  </si>
-  <si>
-    <t>I19</t>
-  </si>
-  <si>
     <t>y1</t>
   </si>
   <si>
@@ -284,45 +167,6 @@
     <t>x6</t>
   </si>
   <si>
-    <t>x7</t>
-  </si>
-  <si>
-    <t>x8</t>
-  </si>
-  <si>
-    <t>x9</t>
-  </si>
-  <si>
-    <t>x10</t>
-  </si>
-  <si>
-    <t>x11</t>
-  </si>
-  <si>
-    <t>x12</t>
-  </si>
-  <si>
-    <t>x13</t>
-  </si>
-  <si>
-    <t>x14</t>
-  </si>
-  <si>
-    <t>x15</t>
-  </si>
-  <si>
-    <t>x16</t>
-  </si>
-  <si>
-    <t>x17</t>
-  </si>
-  <si>
-    <t>x18</t>
-  </si>
-  <si>
-    <t>x19</t>
-  </si>
-  <si>
     <t>y2</t>
   </si>
   <si>
@@ -338,45 +182,6 @@
     <t>y6</t>
   </si>
   <si>
-    <t>y7</t>
-  </si>
-  <si>
-    <t>y8</t>
-  </si>
-  <si>
-    <t>y9</t>
-  </si>
-  <si>
-    <t>y10</t>
-  </si>
-  <si>
-    <t>y11</t>
-  </si>
-  <si>
-    <t>y12</t>
-  </si>
-  <si>
-    <t>y13</t>
-  </si>
-  <si>
-    <t>y14</t>
-  </si>
-  <si>
-    <t>y15</t>
-  </si>
-  <si>
-    <t>y16</t>
-  </si>
-  <si>
-    <t>y17</t>
-  </si>
-  <si>
-    <t>y18</t>
-  </si>
-  <si>
-    <t>y19</t>
-  </si>
-  <si>
     <t>Online</t>
   </si>
   <si>
@@ -386,28 +191,13 @@
     <t>LT3</t>
   </si>
   <si>
-    <t>LT4</t>
-  </si>
-  <si>
-    <t>LT5</t>
-  </si>
-  <si>
-    <t>LT6</t>
-  </si>
-  <si>
-    <t>LT7</t>
-  </si>
-  <si>
-    <t>LT8</t>
-  </si>
-  <si>
-    <t>LT9</t>
-  </si>
-  <si>
-    <t>LT10</t>
-  </si>
-  <si>
-    <t>LT11</t>
+    <t>8:30 - 9:30</t>
+  </si>
+  <si>
+    <t>9:30 - 10:30</t>
+  </si>
+  <si>
+    <t>10:30 - 11:00</t>
   </si>
 </sst>
 </file>
@@ -875,13 +665,13 @@
         <v>13</v>
       </c>
       <c r="F4" t="s">
-        <v>72</v>
+        <v>33</v>
       </c>
       <c r="G4" s="2">
         <v>46322</v>
       </c>
-      <c r="H4" s="3">
-        <v>0.35416666666666669</v>
+      <c r="H4" s="3" t="s">
+        <v>46</v>
       </c>
       <c r="I4" s="3">
         <v>0.4375</v>
@@ -910,13 +700,13 @@
         <v>14</v>
       </c>
       <c r="F5" t="s">
-        <v>90</v>
+        <v>38</v>
       </c>
       <c r="G5" s="2">
         <v>46323</v>
       </c>
-      <c r="H5" s="3">
-        <v>0.39583333333333298</v>
+      <c r="H5" s="3" t="s">
+        <v>47</v>
       </c>
       <c r="I5" s="3">
         <v>0.47916666666666702</v>
@@ -925,7 +715,7 @@
         <v>15</v>
       </c>
       <c r="K5" t="s">
-        <v>109</v>
+        <v>44</v>
       </c>
       <c r="L5" s="2">
         <v>46305</v>
@@ -942,16 +732,16 @@
         <v>23</v>
       </c>
       <c r="E6" t="s">
-        <v>73</v>
+        <v>34</v>
       </c>
       <c r="F6" t="s">
-        <v>91</v>
+        <v>39</v>
       </c>
       <c r="G6" s="2">
         <v>46324</v>
       </c>
-      <c r="H6" s="3">
-        <v>0.4375</v>
+      <c r="H6" s="3" t="s">
+        <v>48</v>
       </c>
       <c r="I6" s="3">
         <v>0.52083333333333304</v>
@@ -960,7 +750,7 @@
         <v>15</v>
       </c>
       <c r="K6" t="s">
-        <v>110</v>
+        <v>45</v>
       </c>
       <c r="L6" s="2">
         <v>46305</v>
@@ -977,22 +767,22 @@
         <v>26</v>
       </c>
       <c r="E7" t="s">
-        <v>74</v>
+        <v>35</v>
       </c>
       <c r="F7" t="s">
-        <v>92</v>
+        <v>40</v>
       </c>
       <c r="G7" s="2">
         <v>46325</v>
       </c>
-      <c r="H7" s="3">
-        <v>0.47916666666666702</v>
+      <c r="H7" s="3" t="s">
+        <v>46</v>
       </c>
       <c r="I7" s="3">
         <v>0.5625</v>
       </c>
       <c r="J7" t="s">
-        <v>108</v>
+        <v>43</v>
       </c>
       <c r="L7" s="2">
         <v>46305</v>
@@ -1009,22 +799,22 @@
         <v>29</v>
       </c>
       <c r="E8" t="s">
-        <v>75</v>
+        <v>36</v>
       </c>
       <c r="F8" t="s">
-        <v>93</v>
+        <v>41</v>
       </c>
       <c r="G8" s="2">
         <v>46326</v>
       </c>
-      <c r="H8" s="3">
-        <v>0.52083333333333304</v>
+      <c r="H8" s="3" t="s">
+        <v>47</v>
       </c>
       <c r="I8" s="3">
         <v>0.60416666666666696</v>
       </c>
       <c r="J8" t="s">
-        <v>108</v>
+        <v>43</v>
       </c>
       <c r="L8" s="2">
         <v>46305</v>
@@ -1041,472 +831,117 @@
         <v>32</v>
       </c>
       <c r="E9" t="s">
-        <v>76</v>
+        <v>37</v>
       </c>
       <c r="F9" t="s">
-        <v>94</v>
+        <v>42</v>
       </c>
       <c r="G9" s="2">
         <v>46327</v>
       </c>
-      <c r="H9" s="3">
-        <v>0.5625</v>
+      <c r="H9" s="3" t="s">
+        <v>48</v>
       </c>
       <c r="I9" s="3">
         <v>0.64583333333333304</v>
       </c>
       <c r="J9" t="s">
-        <v>108</v>
+        <v>43</v>
       </c>
       <c r="L9" s="2">
         <v>46305</v>
       </c>
     </row>
     <row r="10" spans="2:12" ht="17" x14ac:dyDescent="0.25">
-      <c r="B10" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C10" t="s">
-        <v>34</v>
-      </c>
-      <c r="D10" t="s">
-        <v>35</v>
-      </c>
-      <c r="E10" t="s">
-        <v>77</v>
-      </c>
-      <c r="F10" t="s">
-        <v>95</v>
-      </c>
-      <c r="G10" s="2">
-        <v>46328</v>
-      </c>
-      <c r="H10" s="3">
-        <v>0.60416666666666696</v>
-      </c>
-      <c r="I10" s="3">
-        <v>0.6875</v>
-      </c>
-      <c r="J10" t="s">
-        <v>15</v>
-      </c>
-      <c r="K10" t="s">
-        <v>110</v>
-      </c>
-      <c r="L10" s="2">
-        <v>46305</v>
-      </c>
+      <c r="B10" s="1"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="3"/>
+      <c r="I10" s="3"/>
+      <c r="L10" s="2"/>
     </row>
     <row r="11" spans="2:12" ht="17" x14ac:dyDescent="0.25">
-      <c r="B11" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="C11" t="s">
-        <v>37</v>
-      </c>
-      <c r="D11" t="s">
-        <v>38</v>
-      </c>
-      <c r="E11" t="s">
-        <v>78</v>
-      </c>
-      <c r="F11" t="s">
-        <v>96</v>
-      </c>
-      <c r="G11" s="2">
-        <v>46329</v>
-      </c>
-      <c r="H11" s="3">
-        <v>0.64583333333333304</v>
-      </c>
-      <c r="I11" s="3">
-        <v>0.72916666666666696</v>
-      </c>
-      <c r="J11" t="s">
-        <v>15</v>
-      </c>
-      <c r="K11" t="s">
-        <v>111</v>
-      </c>
-      <c r="L11" s="2">
-        <v>46305</v>
-      </c>
+      <c r="B11" s="1"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="3"/>
+      <c r="I11" s="3"/>
+      <c r="L11" s="2"/>
     </row>
     <row r="12" spans="2:12" ht="17" x14ac:dyDescent="0.25">
-      <c r="B12" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="C12" t="s">
-        <v>40</v>
-      </c>
-      <c r="D12" t="s">
-        <v>41</v>
-      </c>
-      <c r="E12" t="s">
-        <v>79</v>
-      </c>
-      <c r="F12" t="s">
-        <v>97</v>
-      </c>
-      <c r="G12" s="2">
-        <v>46330</v>
-      </c>
-      <c r="H12" s="3">
-        <v>0.6875</v>
-      </c>
-      <c r="I12" s="3">
-        <v>0.77083333333333304</v>
-      </c>
-      <c r="J12" t="s">
-        <v>15</v>
-      </c>
-      <c r="K12" t="s">
-        <v>112</v>
-      </c>
-      <c r="L12" s="2">
-        <v>46305</v>
-      </c>
+      <c r="B12" s="1"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="3"/>
+      <c r="I12" s="3"/>
+      <c r="L12" s="2"/>
     </row>
     <row r="13" spans="2:12" ht="17" x14ac:dyDescent="0.25">
-      <c r="B13" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="C13" t="s">
-        <v>43</v>
-      </c>
-      <c r="D13" t="s">
-        <v>44</v>
-      </c>
-      <c r="E13" t="s">
-        <v>80</v>
-      </c>
-      <c r="F13" t="s">
-        <v>98</v>
-      </c>
-      <c r="G13" s="2">
-        <v>46331</v>
-      </c>
-      <c r="H13" s="3">
-        <v>0.72916666666666696</v>
-      </c>
-      <c r="I13" s="3">
-        <v>0.8125</v>
-      </c>
-      <c r="J13" t="s">
-        <v>15</v>
-      </c>
-      <c r="K13" t="s">
-        <v>113</v>
-      </c>
-      <c r="L13" s="2">
-        <v>46305</v>
-      </c>
+      <c r="B13" s="1"/>
+      <c r="G13" s="2"/>
+      <c r="H13" s="3"/>
+      <c r="I13" s="3"/>
+      <c r="L13" s="2"/>
     </row>
     <row r="14" spans="2:12" ht="17" x14ac:dyDescent="0.25">
-      <c r="B14" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="C14" t="s">
-        <v>46</v>
-      </c>
-      <c r="D14" t="s">
-        <v>47</v>
-      </c>
-      <c r="E14" t="s">
-        <v>81</v>
-      </c>
-      <c r="F14" t="s">
-        <v>99</v>
-      </c>
-      <c r="G14" s="2">
-        <v>46332</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0.77083333333333304</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0.85416666666666696</v>
-      </c>
-      <c r="J14" t="s">
-        <v>15</v>
-      </c>
-      <c r="K14" t="s">
-        <v>114</v>
-      </c>
-      <c r="L14" s="2">
-        <v>46305</v>
-      </c>
+      <c r="B14" s="1"/>
+      <c r="G14" s="2"/>
+      <c r="H14" s="3"/>
+      <c r="I14" s="3"/>
+      <c r="L14" s="2"/>
     </row>
     <row r="15" spans="2:12" ht="17" x14ac:dyDescent="0.25">
-      <c r="B15" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C15" t="s">
-        <v>49</v>
-      </c>
-      <c r="D15" t="s">
-        <v>50</v>
-      </c>
-      <c r="E15" t="s">
-        <v>82</v>
-      </c>
-      <c r="F15" t="s">
-        <v>100</v>
-      </c>
-      <c r="G15" s="2">
-        <v>46333</v>
-      </c>
-      <c r="H15" s="3">
-        <v>0.8125</v>
-      </c>
-      <c r="I15" s="3">
-        <v>0.89583333333333304</v>
-      </c>
-      <c r="J15" t="s">
-        <v>108</v>
-      </c>
-      <c r="L15" s="2">
-        <v>46305</v>
-      </c>
+      <c r="B15" s="1"/>
+      <c r="G15" s="2"/>
+      <c r="H15" s="3"/>
+      <c r="I15" s="3"/>
+      <c r="L15" s="2"/>
     </row>
     <row r="16" spans="2:12" ht="17" x14ac:dyDescent="0.25">
-      <c r="B16" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="C16" t="s">
-        <v>52</v>
-      </c>
-      <c r="D16" t="s">
-        <v>53</v>
-      </c>
-      <c r="E16" t="s">
-        <v>83</v>
-      </c>
-      <c r="F16" t="s">
-        <v>101</v>
-      </c>
-      <c r="G16" s="2">
-        <v>46334</v>
-      </c>
-      <c r="H16" s="3">
-        <v>0.85416666666666696</v>
-      </c>
-      <c r="I16" s="3">
-        <v>0.9375</v>
-      </c>
-      <c r="J16" t="s">
-        <v>108</v>
-      </c>
-      <c r="L16" s="2">
-        <v>46305</v>
-      </c>
+      <c r="B16" s="1"/>
+      <c r="G16" s="2"/>
+      <c r="H16" s="3"/>
+      <c r="I16" s="3"/>
+      <c r="L16" s="2"/>
     </row>
     <row r="17" spans="2:12" ht="17" x14ac:dyDescent="0.25">
-      <c r="B17" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="C17" t="s">
-        <v>55</v>
-      </c>
-      <c r="D17" t="s">
-        <v>56</v>
-      </c>
-      <c r="E17" t="s">
-        <v>84</v>
-      </c>
-      <c r="F17" t="s">
-        <v>102</v>
-      </c>
-      <c r="G17" s="2">
-        <v>46335</v>
-      </c>
-      <c r="H17" s="3">
-        <v>0.89583333333333304</v>
-      </c>
-      <c r="I17" s="3">
-        <v>0.97916666666666696</v>
-      </c>
-      <c r="J17" t="s">
-        <v>108</v>
-      </c>
-      <c r="L17" s="2">
-        <v>46305</v>
-      </c>
+      <c r="B17" s="1"/>
+      <c r="G17" s="2"/>
+      <c r="H17" s="3"/>
+      <c r="I17" s="3"/>
+      <c r="L17" s="2"/>
     </row>
     <row r="18" spans="2:12" ht="17" x14ac:dyDescent="0.25">
-      <c r="B18" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C18" t="s">
-        <v>58</v>
-      </c>
-      <c r="D18" t="s">
-        <v>59</v>
-      </c>
-      <c r="E18" t="s">
-        <v>85</v>
-      </c>
-      <c r="F18" t="s">
-        <v>103</v>
-      </c>
-      <c r="G18" s="2">
-        <v>46336</v>
-      </c>
-      <c r="H18" s="3">
-        <v>0.9375</v>
-      </c>
-      <c r="I18" s="3">
-        <v>1.0208333333333299</v>
-      </c>
-      <c r="J18" t="s">
-        <v>15</v>
-      </c>
-      <c r="K18" t="s">
-        <v>114</v>
-      </c>
-      <c r="L18" s="2">
-        <v>46305</v>
-      </c>
+      <c r="B18" s="1"/>
+      <c r="G18" s="2"/>
+      <c r="H18" s="3"/>
+      <c r="I18" s="3"/>
+      <c r="L18" s="2"/>
     </row>
     <row r="19" spans="2:12" ht="17" x14ac:dyDescent="0.25">
-      <c r="B19" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="C19" t="s">
-        <v>61</v>
-      </c>
-      <c r="D19" t="s">
-        <v>62</v>
-      </c>
-      <c r="E19" t="s">
-        <v>86</v>
-      </c>
-      <c r="F19" t="s">
-        <v>104</v>
-      </c>
-      <c r="G19" s="2">
-        <v>46337</v>
-      </c>
-      <c r="H19" s="3">
-        <v>0.97916666666666696</v>
-      </c>
-      <c r="I19" s="3">
-        <v>1.0625</v>
-      </c>
-      <c r="J19" t="s">
-        <v>15</v>
-      </c>
-      <c r="K19" t="s">
-        <v>115</v>
-      </c>
-      <c r="L19" s="2">
-        <v>46305</v>
-      </c>
+      <c r="B19" s="1"/>
+      <c r="G19" s="2"/>
+      <c r="H19" s="3"/>
+      <c r="I19" s="3"/>
+      <c r="L19" s="2"/>
     </row>
     <row r="20" spans="2:12" ht="17" x14ac:dyDescent="0.25">
-      <c r="B20" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="C20" t="s">
-        <v>64</v>
-      </c>
-      <c r="D20" t="s">
-        <v>65</v>
-      </c>
-      <c r="E20" t="s">
-        <v>87</v>
-      </c>
-      <c r="F20" t="s">
-        <v>105</v>
-      </c>
-      <c r="G20" s="2">
-        <v>46338</v>
-      </c>
-      <c r="H20" s="3">
-        <v>1.0208333333333299</v>
-      </c>
-      <c r="I20" s="3">
-        <v>1.1041666666666701</v>
-      </c>
-      <c r="J20" t="s">
-        <v>15</v>
-      </c>
-      <c r="K20" t="s">
-        <v>116</v>
-      </c>
-      <c r="L20" s="2">
-        <v>46305</v>
-      </c>
+      <c r="B20" s="1"/>
+      <c r="G20" s="2"/>
+      <c r="H20" s="3"/>
+      <c r="I20" s="3"/>
+      <c r="L20" s="2"/>
     </row>
     <row r="21" spans="2:12" ht="17" x14ac:dyDescent="0.25">
-      <c r="B21" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="C21" t="s">
-        <v>67</v>
-      </c>
-      <c r="D21" t="s">
-        <v>68</v>
-      </c>
-      <c r="E21" t="s">
-        <v>88</v>
-      </c>
-      <c r="F21" t="s">
-        <v>106</v>
-      </c>
-      <c r="G21" s="2">
-        <v>46339</v>
-      </c>
-      <c r="H21" s="3">
-        <v>1.0625</v>
-      </c>
-      <c r="I21" s="3">
-        <v>1.1458333333333299</v>
-      </c>
-      <c r="J21" t="s">
-        <v>15</v>
-      </c>
-      <c r="K21" t="s">
-        <v>117</v>
-      </c>
-      <c r="L21" s="2">
-        <v>46305</v>
-      </c>
+      <c r="B21" s="1"/>
+      <c r="G21" s="2"/>
+      <c r="H21" s="3"/>
+      <c r="I21" s="3"/>
+      <c r="L21" s="2"/>
     </row>
     <row r="22" spans="2:12" ht="17" x14ac:dyDescent="0.25">
-      <c r="B22" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="C22" t="s">
-        <v>70</v>
-      </c>
-      <c r="D22" t="s">
-        <v>71</v>
-      </c>
-      <c r="E22" t="s">
-        <v>89</v>
-      </c>
-      <c r="F22" t="s">
-        <v>107</v>
-      </c>
-      <c r="G22" s="2">
-        <v>46340</v>
-      </c>
-      <c r="H22" s="3">
-        <v>1.1041666666666701</v>
-      </c>
-      <c r="I22" s="3">
-        <v>1.1875</v>
-      </c>
-      <c r="J22" t="s">
-        <v>15</v>
-      </c>
-      <c r="K22" t="s">
-        <v>118</v>
-      </c>
-      <c r="L22" s="2">
-        <v>46305</v>
-      </c>
+      <c r="B22" s="1"/>
+      <c r="G22" s="2"/>
+      <c r="H22" s="3"/>
+      <c r="I22" s="3"/>
+      <c r="L22" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/catalogue/sessions.xlsx
+++ b/catalogue/sessions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vaibhavgurjar/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9F36A24-C2A8-E94B-A850-1F4FC4165C6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12CA7E70-7486-E34F-9541-5E71F5113279}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="580" windowWidth="28800" windowHeight="16260" xr2:uid="{5C538A93-F245-C740-BD91-3CC6C517ED2A}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="51">
   <si>
     <r>
       <t>Subject</t>
@@ -198,6 +198,12 @@
   </si>
   <si>
     <t>10:30 - 11:00</t>
+  </si>
+  <si>
+    <t>1hr</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
   </si>
 </sst>
 </file>
@@ -673,8 +679,8 @@
       <c r="H4" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="I4" s="3">
-        <v>0.4375</v>
+      <c r="I4" s="3" t="s">
+        <v>49</v>
       </c>
       <c r="J4" t="s">
         <v>15</v>
@@ -708,8 +714,8 @@
       <c r="H5" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="I5" s="3">
-        <v>0.47916666666666702</v>
+      <c r="I5" s="3" t="s">
+        <v>49</v>
       </c>
       <c r="J5" t="s">
         <v>15</v>
@@ -743,8 +749,8 @@
       <c r="H6" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="I6" s="3">
-        <v>0.52083333333333304</v>
+      <c r="I6" s="3" t="s">
+        <v>49</v>
       </c>
       <c r="J6" t="s">
         <v>15</v>
@@ -778,8 +784,8 @@
       <c r="H7" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="I7" s="3">
-        <v>0.5625</v>
+      <c r="I7" s="3" t="s">
+        <v>49</v>
       </c>
       <c r="J7" t="s">
         <v>43</v>
@@ -810,8 +816,8 @@
       <c r="H8" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="I8" s="3">
-        <v>0.60416666666666696</v>
+      <c r="I8" s="3" t="s">
+        <v>49</v>
       </c>
       <c r="J8" t="s">
         <v>43</v>
@@ -842,8 +848,8 @@
       <c r="H9" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="I9" s="3">
-        <v>0.64583333333333304</v>
+      <c r="I9" s="3" t="s">
+        <v>49</v>
       </c>
       <c r="J9" t="s">
         <v>43</v>
@@ -863,7 +869,9 @@
       <c r="B11" s="1"/>
       <c r="G11" s="2"/>
       <c r="H11" s="3"/>
-      <c r="I11" s="3"/>
+      <c r="I11" s="3" t="s">
+        <v>50</v>
+      </c>
       <c r="L11" s="2"/>
     </row>
     <row r="12" spans="2:12" ht="17" x14ac:dyDescent="0.25">
